--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,152 @@
         </is>
       </c>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11:50:22</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E3" t="n">
+        <v>153717</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10593</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I3" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-25</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>832</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>808</v>
+      </c>
+      <c r="R3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>518</v>
+      </c>
+      <c r="T3" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>412</v>
+      </c>
+      <c r="V3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:AT4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,157 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:51:33</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E4" t="n">
+        <v>153674</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10593</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="I4" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>833</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>812</v>
+      </c>
+      <c r="R4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>519</v>
+      </c>
+      <c r="T4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>416</v>
+      </c>
+      <c r="V4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT4"/>
+  <dimension ref="A1:AT5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,157 @@
       <c r="AT4" t="inlineStr">
         <is>
           <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11:57:54</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E5" t="n">
+        <v>153550</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10604</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="I5" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>824</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>826</v>
+      </c>
+      <c r="R5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>506</v>
+      </c>
+      <c r="T5" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>428</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>bullish</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,6 +1245,157 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12:00:07</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>153550</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10604</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="I6" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>825</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>827</v>
+      </c>
+      <c r="R6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>506</v>
+      </c>
+      <c r="T6" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>429</v>
+      </c>
+      <c r="V6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AT7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +1396,157 @@
         </is>
       </c>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12:01:18</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E7" t="n">
+        <v>153555</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10606</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>826</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>825</v>
+      </c>
+      <c r="R7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>506</v>
+      </c>
+      <c r="T7" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>427</v>
+      </c>
+      <c r="V7" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W7" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT7"/>
+  <dimension ref="A1:AT8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,157 @@
         </is>
       </c>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12:04:53</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E8" t="n">
+        <v>153535</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10615</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="I8" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>829</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>827</v>
+      </c>
+      <c r="R8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>506</v>
+      </c>
+      <c r="T8" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>427</v>
+      </c>
+      <c r="V8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT8"/>
+  <dimension ref="A1:AT9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1698,6 +1698,152 @@
         </is>
       </c>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12:07:03</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E9" t="n">
+        <v>153590</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10623</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="I9" t="n">
+        <v>153500</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>829</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>827</v>
+      </c>
+      <c r="R9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>506</v>
+      </c>
+      <c r="T9" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>427</v>
+      </c>
+      <c r="V9" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>154000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
         <is>
           <t>bullish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT9"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1846,6 +1846,148 @@
       <c r="AT9" t="inlineStr">
         <is>
           <t>bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>17:21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>153926</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10704</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="I10" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>884</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>861</v>
+      </c>
+      <c r="R10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>570</v>
+      </c>
+      <c r="T10" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>425</v>
+      </c>
+      <c r="V10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>bearish</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT10"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1986,6 +1986,157 @@
         </is>
       </c>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17:22:39</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E11" t="n">
+        <v>153972</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10705</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="I11" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>22</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>883</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>864</v>
+      </c>
+      <c r="R11" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>570</v>
+      </c>
+      <c r="T11" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>429</v>
+      </c>
+      <c r="V11" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT11"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,157 @@
         </is>
       </c>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>17:23:45</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E12" t="n">
+        <v>153890</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10703</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="I12" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>22</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>883</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>864</v>
+      </c>
+      <c r="R12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>570</v>
+      </c>
+      <c r="T12" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>429</v>
+      </c>
+      <c r="V12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT12"/>
+  <dimension ref="A1:AT13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,6 +2288,157 @@
         </is>
       </c>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>17:24:53</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E13" t="n">
+        <v>153890</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10703</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="I13" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>883</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>863</v>
+      </c>
+      <c r="R13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>570</v>
+      </c>
+      <c r="T13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>429</v>
+      </c>
+      <c r="V13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT13"/>
+  <dimension ref="A1:AT14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2439,6 +2439,157 @@
         </is>
       </c>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>17:26:01</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>154000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10716</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="I14" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>21</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>883</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>863</v>
+      </c>
+      <c r="R14" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>571</v>
+      </c>
+      <c r="T14" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>427</v>
+      </c>
+      <c r="V14" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT14"/>
+  <dimension ref="A1:AT15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2590,6 +2590,162 @@
         </is>
       </c>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>17:27:08</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E15" t="n">
+        <v>154023</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10720</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="I15" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>883</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>863</v>
+      </c>
+      <c r="R15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>571</v>
+      </c>
+      <c r="T15" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>427</v>
+      </c>
+      <c r="V15" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT15"/>
+  <dimension ref="A1:AT16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,6 +2746,162 @@
         </is>
       </c>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>17:28:16</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>154195</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10734</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="I16" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>896</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>862</v>
+      </c>
+      <c r="R16" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>583</v>
+      </c>
+      <c r="T16" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>425</v>
+      </c>
+      <c r="V16" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT16"/>
+  <dimension ref="A1:AT17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2902,6 +2902,157 @@
         </is>
       </c>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>17:29:23</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>154319</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10741</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="I17" t="n">
+        <v>154500</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-21</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>882</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>861</v>
+      </c>
+      <c r="R17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>579</v>
+      </c>
+      <c r="T17" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>424</v>
+      </c>
+      <c r="V17" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>

--- a/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
+++ b/backend/signal_logs/2026-09-03/index_tracker_GOLD_2026-09-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT17"/>
+  <dimension ref="A1:AT18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3053,6 +3053,162 @@
         </is>
       </c>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17:30:29</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>154200</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10736</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>154000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>21</v>
+      </c>
+      <c r="N18" t="n">
+        <v>21</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>892</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>858</v>
+      </c>
+      <c r="R18" t="n">
+        <v>150000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>577</v>
+      </c>
+      <c r="T18" t="n">
+        <v>155000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>421</v>
+      </c>
+      <c r="V18" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="W18" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>155000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>bearish</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>bullish</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
         <is>
           <t>bearish</t>
         </is>
